--- a/data/export/2026-09-24-operations.xlsx
+++ b/data/export/2026-09-24-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +828,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -908,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -947,7 +963,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -958,7 +974,7 @@
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1040,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1074,7 +1090,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1123,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1140,7 +1160,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1184,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1204,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1280,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1330,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1396,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1446,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1512,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1562,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1575,22 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1623,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1642,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1678,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1720,7 +1744,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1758,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1794,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1836,7 +1860,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1874,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1910,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1952,7 +1976,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1990,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2015,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2091,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2110,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2118,35 +2146,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2184,7 +2212,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2226,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2223,7 +2251,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2234,7 +2262,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -2247,22 +2275,22 @@
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>06:41</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2323,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2342,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2350,7 +2378,7 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -2363,22 +2391,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2416,7 +2444,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2458,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2466,7 +2494,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2507,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2555,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2574,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,35 +2610,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2643,12 +2671,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2690,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2726,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2759,12 +2787,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2806,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2842,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2903,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2922,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,35 +2958,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2991,12 +3019,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3010,7 +3038,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3046,7 +3074,2791 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A37970D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-operations.xlsx
+++ b/data/export/2026-09-24-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD46"/>
+  <dimension ref="A1:AD79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -653,19 +653,19 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -777,24 +777,24 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,22 +843,22 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -891,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -924,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -948,17 +952,17 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -968,13 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1007,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1040,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1064,33 +1076,37 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1133,24 +1149,24 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1160,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1199,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1247,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1280,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1304,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1396,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1420,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1479,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1512,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1536,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1667,7 +1707,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1678,7 +1718,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1711,32 +1751,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1744,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1768,33 +1812,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1908,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1910,7 +1958,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1976,7 +2024,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2025,12 +2073,12 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2144,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2146,7 +2194,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2159,22 +2207,22 @@
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>07:55</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2207,12 +2255,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2226,7 +2274,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2251,7 +2299,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2262,35 +2310,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2328,7 +2376,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2342,7 +2390,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2367,46 +2415,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2496,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2458,7 +2510,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2483,46 +2535,50 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2560,7 +2616,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2574,7 +2630,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2599,46 +2655,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2676,7 +2736,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2690,7 +2750,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2715,46 +2775,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2787,12 +2851,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2806,7 +2870,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2842,35 +2906,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2903,12 +2967,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2922,7 +2986,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2947,46 +3011,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3024,7 +3092,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3038,7 +3106,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3063,46 +3131,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3135,12 +3207,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3154,7 +3226,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3179,46 +3251,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3251,12 +3327,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3270,7 +3346,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3295,7 +3371,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3306,35 +3382,35 @@
       <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3367,12 +3443,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3386,7 +3462,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3411,18 +3487,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3515,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3445,7 +3525,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3455,40 +3535,44 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3502,7 +3586,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3512,33 +3596,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3639,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3561,7 +3649,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3571,40 +3659,44 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3618,7 +3710,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3628,33 +3720,37 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -3667,60 +3763,64 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3734,7 +3834,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3744,17 +3844,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3764,13 +3864,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3887,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3793,7 +3897,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3831,12 +3935,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3850,7 +3954,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3875,7 +3979,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3886,7 +3990,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3899,7 +4003,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3909,7 +4013,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3919,12 +4023,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq38，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3947,12 +4051,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3960,13 +4064,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4002,7 +4122,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4135,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4025,7 +4145,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4063,12 +4183,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4082,7 +4202,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4118,7 +4238,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4251,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4141,7 +4261,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4179,12 +4299,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4198,7 +4318,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4234,35 +4354,35 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4295,12 +4415,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4314,7 +4434,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4350,35 +4470,35 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4411,12 +4531,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4430,7 +4550,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4466,35 +4586,35 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4527,12 +4647,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4546,7 +4666,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4582,35 +4702,35 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4643,12 +4763,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4662,7 +4782,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4698,35 +4818,35 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4759,12 +4879,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4778,7 +4898,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4814,35 +4934,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4875,12 +4995,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4894,7 +5014,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4930,35 +5050,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4991,12 +5111,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5010,7 +5130,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5046,35 +5166,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5107,12 +5227,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5126,7 +5246,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5162,35 +5282,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5223,12 +5343,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5242,7 +5362,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5278,35 +5398,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5339,12 +5459,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5358,7 +5478,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5394,35 +5514,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5455,12 +5575,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5474,7 +5594,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5510,35 +5630,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A37970D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5571,12 +5691,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5590,7 +5710,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5626,35 +5746,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5687,12 +5807,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5706,7 +5826,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5742,35 +5862,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5803,12 +5923,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5822,7 +5942,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5858,7 +5978,3891 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>3/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>1/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>108分钟</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>108.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>106分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>97分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A37970D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A66631D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>108.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-operations.xlsx
+++ b/data/export/2026-09-24-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD79"/>
+  <dimension ref="A1:AD100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,17 +967,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1635,32 +1635,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1668,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1692,17 +1696,17 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1712,13 +1716,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1769,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -1788,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1837,12 +1845,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1875,32 +1883,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1908,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1932,33 +1944,37 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1991,32 +2007,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2024,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2048,37 +2068,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2111,32 +2131,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2144,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2168,33 +2192,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2227,32 +2255,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2260,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2284,33 +2316,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2343,32 +2379,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2376,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2400,32 +2440,32 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2463,32 +2503,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2496,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2520,17 +2564,17 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2540,17 +2584,17 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2583,32 +2627,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2616,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2640,37 +2688,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2784,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2790,7 +2838,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2904,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2972,7 +3020,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3026,7 +3074,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3140,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3146,7 +3194,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3260,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3266,7 +3314,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3380,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3376,13 +3424,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3500,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3497,74 +3549,70 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3572,7 +3620,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3586,7 +3634,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3596,17 +3644,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3621,74 +3669,70 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3696,7 +3740,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3710,7 +3754,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3720,107 +3764,103 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3834,7 +3874,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3844,65 +3884,65 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3935,12 +3975,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3954,7 +3994,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3984,51 +4024,55 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq38，推进9站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4056,7 +4100,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4064,29 +4108,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>物理seq28（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>07:51</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4111,46 +4139,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4183,12 +4215,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4202,7 +4234,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4227,18 +4259,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4287,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4261,7 +4297,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4271,32 +4307,36 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4304,7 +4344,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4318,7 +4358,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4328,33 +4368,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -4367,7 +4411,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4377,7 +4421,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4387,40 +4431,44 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4434,7 +4482,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4444,33 +4492,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -4483,60 +4535,64 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4550,7 +4606,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4560,33 +4616,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -4599,22 +4659,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4647,12 +4707,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4666,7 +4726,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4691,7 +4751,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4715,32 +4775,32 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq59，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4763,12 +4823,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4776,13 +4836,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4807,7 +4883,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4831,7 +4907,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4841,7 +4917,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4851,40 +4927,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4898,7 +4978,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4908,33 +4988,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -4947,7 +5031,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4957,7 +5041,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4995,12 +5079,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5014,7 +5098,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5039,7 +5123,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -5063,60 +5147,64 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5130,7 +5218,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5140,33 +5228,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -5179,22 +5271,22 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5227,12 +5319,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5246,7 +5338,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5295,7 +5387,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5305,7 +5397,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5343,12 +5435,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5362,7 +5454,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5387,7 +5479,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5411,7 +5503,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5421,7 +5513,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5459,12 +5551,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5478,7 +5570,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5527,7 +5619,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5537,7 +5629,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5575,12 +5667,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5594,7 +5686,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5643,7 +5735,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5653,7 +5745,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5691,12 +5783,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5710,7 +5802,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5759,7 +5851,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5769,7 +5861,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5807,12 +5899,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5826,7 +5918,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5875,7 +5967,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5885,7 +5977,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5923,12 +6015,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5942,7 +6034,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5991,7 +6083,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6001,7 +6093,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6039,12 +6131,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6058,7 +6150,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6107,7 +6199,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6117,7 +6209,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6155,12 +6247,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6174,7 +6266,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6223,7 +6315,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6233,7 +6325,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6271,12 +6363,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6290,7 +6382,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6339,7 +6431,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6349,7 +6441,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6387,12 +6479,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6406,7 +6498,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6455,22 +6547,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6508,7 +6600,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6522,7 +6614,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6547,22 +6639,18 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>142.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -6575,22 +6663,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:54</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6623,12 +6711,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6642,7 +6730,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6667,22 +6755,18 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -6695,7 +6779,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6705,7 +6789,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6748,7 +6832,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6762,7 +6846,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6787,7 +6871,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6805,28 +6889,28 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6859,12 +6943,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6878,7 +6962,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6903,7 +6987,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6914,77 +6998,73 @@
       <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>108分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6998,7 +7078,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7008,107 +7088,99 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>108.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>106分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7122,7 +7194,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7132,107 +7204,99 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7246,7 +7310,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7256,17 +7320,17 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7281,82 +7345,78 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7370,7 +7430,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7380,17 +7440,17 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7405,40 +7465,40 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7471,12 +7531,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7490,7 +7550,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7526,35 +7586,35 @@
       <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7587,12 +7647,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7606,7 +7666,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7631,46 +7691,50 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7703,12 +7767,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7722,7 +7786,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7758,35 +7822,35 @@
       <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7819,12 +7883,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7838,7 +7902,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7863,7 +7927,7 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
@@ -7874,35 +7938,35 @@
       <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7935,12 +7999,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7954,7 +8018,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7984,41 +8048,45 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8051,12 +8119,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8070,7 +8138,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8095,46 +8163,50 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8167,12 +8239,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8186,7 +8258,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8211,7 +8283,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8222,7 +8294,7 @@
       <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8307,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A37970D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8245,7 +8317,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8283,12 +8355,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8302,7 +8374,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8327,18 +8399,22 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8427,7 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8361,7 +8437,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8371,40 +8447,44 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8418,7 +8498,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8428,33 +8508,37 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>108.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8467,52 +8551,56 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8520,7 +8608,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8534,7 +8622,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8544,33 +8632,37 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8583,60 +8675,64 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A66631D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8650,7 +8746,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8660,33 +8756,37 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8799,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8709,7 +8809,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8719,40 +8819,44 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8766,7 +8870,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8776,17 +8880,17 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8796,13 +8900,17 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8815,7 +8923,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8825,7 +8933,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8863,12 +8971,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8882,7 +8990,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8907,7 +9015,7 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -8931,22 +9039,22 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>08:14</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8979,12 +9087,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8998,7 +9106,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9028,17 +9136,13 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>108.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9051,52 +9155,56 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9104,7 +9212,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9118,7 +9226,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9128,17 +9236,17 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9153,12 +9261,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9171,7 +9279,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9181,7 +9289,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9191,40 +9299,44 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9238,7 +9350,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9248,17 +9360,17 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9273,12 +9385,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9403,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9301,7 +9413,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9311,40 +9423,44 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9358,7 +9474,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9368,17 +9484,17 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9393,12 +9509,12 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9411,22 +9527,22 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -9459,12 +9575,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9478,7 +9594,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9503,7 +9619,7 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
@@ -9527,60 +9643,64 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9594,7 +9714,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9604,17 +9724,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9624,13 +9744,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9643,52 +9767,56 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A37970D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -9696,7 +9824,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9710,7 +9838,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9720,17 +9848,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9740,13 +9868,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC78" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9891,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -9769,7 +9901,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -9807,7 +9939,7 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9826,7 +9958,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9851,7 +9983,7 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
@@ -9863,6 +9995,2506 @@
       <c r="AD79" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A66631D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>108.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A37970D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A66631D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>108.0</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-operations.xlsx
+++ b/data/export/2026-09-24-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD185"/>
+  <dimension ref="A1:AD186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -12202,7 +12202,7 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -12272,7 +12272,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -13857,24 +13857,24 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr"/>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13933,7 +13933,7 @@
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AD109" s="2" t="inlineStr">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq44，推进6站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq47，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -14004,7 +14004,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14136,7 +14136,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14848,7 +14848,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15328,7 +15328,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -15448,7 +15448,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15568,7 +15568,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15928,7 +15928,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -16540,7 +16540,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16664,7 +16664,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="AA135" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB135" s="2" t="inlineStr">
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17520,7 +17520,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17569,7 +17569,7 @@
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
@@ -17768,7 +17768,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18140,7 +18140,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -18872,7 +18872,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19360,7 +19360,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19399,7 +19399,7 @@
       </c>
       <c r="AA154" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB154" s="2" t="inlineStr">
@@ -19409,7 +19409,7 @@
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19608,7 +19608,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19657,7 +19657,7 @@
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
@@ -19852,7 +19852,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -19976,7 +19976,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20030,7 +20030,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -20220,7 +20220,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20468,7 +20468,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20712,7 +20712,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -20832,7 +20832,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="AA166" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB166" s="2" t="inlineStr">
@@ -20881,7 +20881,7 @@
       </c>
       <c r="AC166" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD166" s="2" t="inlineStr">
@@ -20956,7 +20956,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21005,7 +21005,7 @@
       </c>
       <c r="AC167" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD167" s="2" t="inlineStr">
@@ -21076,7 +21076,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21324,7 +21324,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21378,7 +21378,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21696,7 +21696,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21820,7 +21820,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -21917,12 +21917,12 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr"/>
@@ -21944,7 +21944,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -21983,7 +21983,7 @@
       </c>
       <c r="AA175" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB175" s="2" t="inlineStr">
@@ -21993,7 +21993,7 @@
       </c>
       <c r="AC175" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD175" s="2" t="inlineStr">
@@ -22041,12 +22041,12 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
@@ -22068,7 +22068,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22117,7 +22117,7 @@
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
@@ -22188,7 +22188,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22308,7 +22308,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22428,7 +22428,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22482,7 +22482,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -22548,7 +22548,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22668,7 +22668,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22788,7 +22788,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -22908,7 +22908,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23095,22 +23095,22 @@
       <c r="B185" s="2" t="inlineStr"/>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E185" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="F185" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -23143,12 +23143,12 @@
       <c r="N185" s="2" t="inlineStr"/>
       <c r="O185" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23187,16 +23187,136 @@
       </c>
       <c r="AA185" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB185" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB185" s="2" t="inlineStr">
+      <c r="AC185" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AD185" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr"/>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr"/>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr"/>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P186" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R186" s="2" t="inlineStr"/>
+      <c r="S186" s="2" t="inlineStr"/>
+      <c r="T186" s="2" t="inlineStr"/>
+      <c r="U186" s="2" t="inlineStr"/>
+      <c r="V186" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="W186" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X186" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y186" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z186" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA186" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB186" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC185" s="2" t="inlineStr"/>
-      <c r="AD185" s="2" t="inlineStr">
+      <c r="AC186" s="2" t="inlineStr"/>
+      <c r="AD186" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-09-24-operations.xlsx
+++ b/data/export/2026-09-24-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1468,17 +1468,17 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2088,17 +2088,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2212,17 +2212,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2460,17 +2460,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3204,17 +3204,17 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3824,17 +3824,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3948,17 +3948,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4196,17 +4196,17 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5312,17 +5312,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5436,17 +5436,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5560,17 +5560,17 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6428,17 +6428,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -7048,17 +7048,17 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7420,17 +7420,17 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7916,17 +7916,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8040,17 +8040,17 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8536,17 +8536,17 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8784,17 +8784,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9280,17 +9280,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9600,7 +9600,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9644,12 +9644,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
@@ -9902,7 +9902,7 @@
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10016,17 +10016,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10264,17 +10264,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10344,7 +10344,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10636,17 +10636,17 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -11004,17 +11004,17 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11376,12 +11376,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
@@ -11419,32 +11419,36 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11452,7 +11456,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11476,17 +11480,17 @@
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
@@ -11496,17 +11500,17 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -11576,7 +11580,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11663,32 +11667,36 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11696,7 +11704,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11720,17 +11728,17 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
@@ -11740,12 +11748,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
@@ -11783,32 +11791,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11816,7 +11828,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11840,17 +11852,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11860,17 +11872,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11903,32 +11915,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11936,7 +11952,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11960,17 +11976,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11980,17 +11996,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -12023,32 +12039,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12056,7 +12076,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12080,17 +12100,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12100,17 +12120,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -12143,32 +12163,36 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -12176,7 +12200,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12200,17 +12224,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -12220,12 +12244,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12296,7 +12320,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12416,7 +12440,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12460,17 +12484,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -12540,7 +12564,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12589,12 +12613,12 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12688,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12718,7 +12742,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -12962,7 +12986,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -13164,7 +13188,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13218,7 +13242,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -13284,7 +13308,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13328,17 +13352,17 @@
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -13462,7 +13486,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -13582,7 +13606,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13676,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13772,7 +13796,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13816,12 +13840,12 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
@@ -13950,7 +13974,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -14020,7 +14044,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14074,7 +14098,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14168,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14188,17 +14212,17 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -14268,7 +14292,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14322,7 +14346,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -14566,7 +14590,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -14806,7 +14830,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -14872,7 +14896,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14916,13 +14940,17 @@
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC117" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC117" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -14992,7 +15020,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15041,12 +15069,12 @@
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -15240,7 +15268,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15294,7 +15322,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -15364,7 +15392,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15418,7 +15446,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -15488,7 +15516,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15532,17 +15560,17 @@
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -15612,7 +15640,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15661,12 +15689,12 @@
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -15736,7 +15764,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15790,7 +15818,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15942,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -16236,7 +16264,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16280,17 +16308,17 @@
       </c>
       <c r="AB128" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC128" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -16360,7 +16388,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16414,7 +16442,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -16538,7 +16566,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -16662,7 +16690,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -16732,7 +16760,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16856,7 +16884,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16900,12 +16928,12 @@
       </c>
       <c r="AB133" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC133" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AD133" s="2" t="inlineStr">
@@ -17034,7 +17062,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -17104,7 +17132,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17158,7 +17186,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -17228,7 +17256,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17282,7 +17310,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -17352,7 +17380,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17396,17 +17424,17 @@
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -17778,7 +17806,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -17848,7 +17876,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17897,12 +17925,12 @@
       </c>
       <c r="AC141" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -17972,7 +18000,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18026,7 +18054,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -18150,7 +18178,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -18274,7 +18302,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -18344,7 +18372,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18398,7 +18426,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18550,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -18712,7 +18740,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -18902,7 +18930,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -19026,7 +19054,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -19096,7 +19124,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -19150,7 +19178,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -19274,7 +19302,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -19344,7 +19372,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19388,17 +19416,17 @@
       </c>
       <c r="AB153" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC153" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -19468,7 +19496,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19517,12 +19545,12 @@
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -19646,7 +19674,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -19766,7 +19794,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -19832,7 +19860,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19886,7 +19914,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -20134,7 +20162,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20232,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20253,12 +20281,12 @@
       </c>
       <c r="AC160" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20410,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -20452,7 +20480,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20496,17 +20524,17 @@
       </c>
       <c r="AB162" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC162" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -20572,7 +20600,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20616,13 +20644,17 @@
       </c>
       <c r="AB163" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC163" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC163" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -20828,7 +20860,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -20872,12 +20904,12 @@
       </c>
       <c r="AB165" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC165" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AD165" s="2" t="inlineStr">
@@ -20948,7 +20980,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -20992,17 +21024,17 @@
       </c>
       <c r="AB166" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC166" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -21072,7 +21104,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21126,7 +21158,7 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -21192,7 +21224,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21312,7 +21344,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21366,7 +21398,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -21432,7 +21464,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21486,7 +21518,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -21556,7 +21588,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21610,7 +21642,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -21680,7 +21712,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21734,7 +21766,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -21924,7 +21956,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22102,7 +22134,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22328,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22350,7 +22382,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -22474,7 +22506,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -22594,7 +22626,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -22637,24 +22669,24 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr"/>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N180" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O180" s="2" t="inlineStr">
@@ -22664,7 +22696,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22713,12 +22745,12 @@
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -22761,24 +22793,24 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr"/>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N181" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O181" s="2" t="inlineStr">
@@ -22788,7 +22820,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22837,12 +22869,12 @@
       </c>
       <c r="AC181" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -22875,32 +22907,36 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr"/>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N182" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22908,7 +22944,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -22932,17 +22968,17 @@
       </c>
       <c r="X182" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z182" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA182" s="2" t="inlineStr">
@@ -22952,17 +22988,17 @@
       </c>
       <c r="AB182" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC182" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -22995,32 +23031,36 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N183" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23028,7 +23068,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23052,17 +23092,17 @@
       </c>
       <c r="X183" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA183" s="2" t="inlineStr">
@@ -23072,13 +23112,17 @@
       </c>
       <c r="AB183" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC183" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC183" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -23111,32 +23155,36 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr"/>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N184" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -23144,7 +23192,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23168,17 +23216,17 @@
       </c>
       <c r="X184" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z184" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA184" s="2" t="inlineStr">
@@ -23188,17 +23236,17 @@
       </c>
       <c r="AB184" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC184" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -23231,32 +23279,36 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr"/>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N185" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23264,7 +23316,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23288,17 +23340,17 @@
       </c>
       <c r="X185" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z185" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA185" s="2" t="inlineStr">
@@ -23308,17 +23360,17 @@
       </c>
       <c r="AB185" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC185" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -23384,7 +23436,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23438,7 +23490,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -23471,32 +23523,36 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr"/>
       <c r="M187" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N187" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -23504,7 +23560,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23528,17 +23584,17 @@
       </c>
       <c r="X187" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z187" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA187" s="2" t="inlineStr">
@@ -23548,12 +23604,12 @@
       </c>
       <c r="AB187" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC187" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AD187" s="2" t="inlineStr">
@@ -23624,7 +23680,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23678,7 +23734,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -23711,12 +23767,12 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq51，推进23站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
@@ -23744,7 +23800,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23752,10 +23808,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R189" s="2" t="inlineStr"/>
-      <c r="S189" s="2" t="inlineStr"/>
-      <c r="T189" s="2" t="inlineStr"/>
-      <c r="U189" s="2" t="inlineStr"/>
+      <c r="R189" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S189" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="T189" s="2" t="inlineStr">
+        <is>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="U189" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V189" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -23798,7 +23870,7 @@
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -23864,7 +23936,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23918,7 +23990,7 @@
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -23984,7 +24056,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24038,7 +24110,7 @@
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -24104,7 +24176,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24158,7 +24230,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -24224,7 +24296,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24278,7 +24350,7 @@
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -24344,7 +24416,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24464,7 +24536,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24518,7 +24590,7 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24656,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24638,7 +24710,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -25080,7 +25152,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25124,17 +25196,17 @@
       </c>
       <c r="AB200" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -25200,7 +25272,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25244,17 +25316,17 @@
       </c>
       <c r="AB201" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25446,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -25498,7 +25570,7 @@
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -25568,7 +25640,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25612,12 +25684,12 @@
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
@@ -25692,7 +25764,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25736,17 +25808,17 @@
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25938,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -25936,7 +26008,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -25980,17 +26052,17 @@
       </c>
       <c r="AB207" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -26114,7 +26186,7 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -26358,7 +26430,7 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -26552,7 +26624,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26606,7 +26678,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -26730,7 +26802,7 @@
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -27048,7 +27120,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27092,17 +27164,17 @@
       </c>
       <c r="AB216" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC216" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -27346,7 +27418,7 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -27466,7 +27538,7 @@
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -27536,7 +27608,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27580,17 +27652,17 @@
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -27710,7 +27782,7 @@
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -27776,7 +27848,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27820,17 +27892,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -27896,7 +27968,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -27940,12 +28012,12 @@
       </c>
       <c r="AB223" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC223" s="2" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AD223" s="2" t="inlineStr">
@@ -28020,7 +28092,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28064,17 +28136,17 @@
       </c>
       <c r="AB224" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -28198,7 +28270,7 @@
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -28322,7 +28394,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -28446,7 +28518,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -28880,7 +28952,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -28936,17 +29008,17 @@
       </c>
       <c r="AB231" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -29194,7 +29266,7 @@
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -29318,7 +29390,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -29384,7 +29456,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q235" s="2" t="inlineStr">
@@ -29440,17 +29512,17 @@
       </c>
       <c r="AB235" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC235" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -29520,7 +29592,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29564,17 +29636,17 @@
       </c>
       <c r="AB236" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -29694,7 +29766,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -29818,7 +29890,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -29938,7 +30010,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -30434,7 +30506,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -30558,7 +30630,7 @@
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -30628,7 +30700,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q245" s="2" t="inlineStr">
@@ -30672,17 +30744,17 @@
       </c>
       <c r="AB245" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC245" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -30806,7 +30878,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -30930,7 +31002,7 @@
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -31054,7 +31126,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -31496,7 +31568,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q252" s="2" t="inlineStr">
@@ -31550,7 +31622,7 @@
       </c>
       <c r="AD252" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31746,7 @@
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -31798,7 +31870,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -32042,7 +32114,7 @@
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -32112,7 +32184,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q257" s="2" t="inlineStr">
@@ -32156,17 +32228,17 @@
       </c>
       <c r="AB257" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC257" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -32236,7 +32308,7 @@
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q258" s="2" t="inlineStr">
@@ -32280,17 +32352,17 @@
       </c>
       <c r="AB258" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC258" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -32414,7 +32486,7 @@
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -32480,7 +32552,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32524,12 +32596,12 @@
       </c>
       <c r="AB260" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
@@ -32654,7 +32726,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -32774,7 +32846,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -32844,7 +32916,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -32888,17 +32960,17 @@
       </c>
       <c r="AB263" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -33216,7 +33288,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33260,17 +33332,17 @@
       </c>
       <c r="AB266" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -33394,7 +33466,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -33588,7 +33660,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33642,7 +33714,7 @@
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -33890,7 +33962,7 @@
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -33960,7 +34032,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34004,17 +34076,17 @@
       </c>
       <c r="AB272" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -34138,7 +34210,7 @@
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -34208,7 +34280,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34252,17 +34324,17 @@
       </c>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -34386,7 +34458,7 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -34506,7 +34578,7 @@
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -34576,7 +34648,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
@@ -34620,12 +34692,12 @@
       </c>
       <c r="AB277" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC277" s="2" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AD277" s="2" t="inlineStr">
@@ -34696,7 +34768,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34740,17 +34812,17 @@
       </c>
       <c r="AB278" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC278" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -34874,7 +34946,7 @@
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -35064,7 +35136,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35108,17 +35180,17 @@
       </c>
       <c r="AB281" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -35606,7 +35678,7 @@
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -35676,7 +35748,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35730,7 +35802,7 @@
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -35978,7 +36050,7 @@
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -36102,7 +36174,7 @@
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -36135,32 +36207,36 @@
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K290" s="2" t="inlineStr"/>
       <c r="L290" s="2" t="inlineStr"/>
       <c r="M290" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N290" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N290" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O290" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -36168,7 +36244,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
@@ -36192,17 +36268,17 @@
       </c>
       <c r="X290" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y290" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z290" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA290" s="2" t="inlineStr">
@@ -36212,17 +36288,17 @@
       </c>
       <c r="AB290" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC290" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -36255,32 +36331,36 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K291" s="2" t="inlineStr"/>
       <c r="L291" s="2" t="inlineStr"/>
       <c r="M291" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N291" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N291" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O291" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -36288,7 +36368,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q291" s="2" t="inlineStr">
@@ -36312,17 +36392,17 @@
       </c>
       <c r="X291" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y291" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z291" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA291" s="2" t="inlineStr">
@@ -36332,17 +36412,17 @@
       </c>
       <c r="AB291" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC291" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -36375,32 +36455,36 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K292" s="2" t="inlineStr"/>
       <c r="L292" s="2" t="inlineStr"/>
       <c r="M292" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N292" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N292" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O292" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -36408,7 +36492,7 @@
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q292" s="2" t="inlineStr">
@@ -36432,17 +36516,17 @@
       </c>
       <c r="X292" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y292" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z292" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA292" s="2" t="inlineStr">
@@ -36452,17 +36536,17 @@
       </c>
       <c r="AB292" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC292" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -36495,32 +36579,36 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K293" s="2" t="inlineStr"/>
       <c r="L293" s="2" t="inlineStr"/>
       <c r="M293" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N293" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N293" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O293" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -36528,7 +36616,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36552,17 +36640,17 @@
       </c>
       <c r="X293" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y293" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z293" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA293" s="2" t="inlineStr">
@@ -36572,12 +36660,12 @@
       </c>
       <c r="AB293" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
@@ -36615,32 +36703,36 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K294" s="2" t="inlineStr"/>
       <c r="L294" s="2" t="inlineStr"/>
       <c r="M294" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N294" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N294" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O294" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -36648,7 +36740,7 @@
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q294" s="2" t="inlineStr">
@@ -36672,17 +36764,17 @@
       </c>
       <c r="X294" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y294" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z294" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA294" s="2" t="inlineStr">
@@ -36692,17 +36784,17 @@
       </c>
       <c r="AB294" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC294" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -36768,7 +36860,7 @@
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q295" s="2" t="inlineStr">
@@ -36822,7 +36914,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -36888,7 +36980,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -36932,17 +37024,17 @@
       </c>
       <c r="AB296" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -37008,7 +37100,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37052,12 +37144,12 @@
       </c>
       <c r="AB297" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC297" s="2" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AD297" s="2" t="inlineStr">

--- a/data/export/2026-09-24-operations.xlsx
+++ b/data/export/2026-09-24-operations.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -11332,7 +11332,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11624,12 +11624,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -12185,12 +12185,12 @@
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12287,32 +12287,36 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12320,7 +12324,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12344,17 +12348,17 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
@@ -12364,12 +12368,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
@@ -12440,7 +12444,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12688,7 +12692,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12732,17 +12736,17 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -12986,7 +12990,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13192,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13232,17 +13236,17 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13366,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -13676,7 +13680,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13730,7 +13734,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -13974,7 +13978,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -14044,7 +14048,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14088,17 +14092,17 @@
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -14222,7 +14226,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14296,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -15074,7 +15078,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -15198,7 +15202,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -15268,7 +15272,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15322,7 +15326,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -15392,7 +15396,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15436,17 +15440,17 @@
       </c>
       <c r="AB121" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC121" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -15570,7 +15574,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -15764,7 +15768,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15808,17 +15812,17 @@
       </c>
       <c r="AB124" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC124" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -15942,7 +15946,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -16318,7 +16322,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -16388,7 +16392,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16432,17 +16436,17 @@
       </c>
       <c r="AB129" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC129" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -16760,7 +16764,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16814,7 +16818,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -17062,7 +17066,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -17132,7 +17136,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17176,17 +17180,17 @@
       </c>
       <c r="AB135" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -17256,7 +17260,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17434,7 +17438,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -17930,7 +17934,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -18000,7 +18004,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18044,17 +18048,17 @@
       </c>
       <c r="AB142" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -18302,7 +18306,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -18372,7 +18376,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18426,7 +18430,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -19178,7 +19182,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -19302,7 +19306,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -19426,7 +19430,7 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -19550,7 +19554,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -19794,7 +19798,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -19860,7 +19864,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19904,17 +19908,17 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -20038,7 +20042,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -20534,7 +20538,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21038,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -21104,7 +21108,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21148,17 +21152,17 @@
       </c>
       <c r="AB167" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC167" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -21398,7 +21402,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -21464,7 +21468,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21518,7 +21522,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -21588,7 +21592,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21632,17 +21636,17 @@
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -21712,7 +21716,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21756,17 +21760,17 @@
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21960,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22010,7 +22014,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -22258,7 +22262,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -22328,7 +22332,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22506,7 +22510,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -22874,7 +22878,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -22998,7 +23002,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -23246,7 +23250,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -23370,7 +23374,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -23436,7 +23440,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23490,7 +23494,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -23734,7 +23738,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -23772,7 +23776,7 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq51，推进23站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
@@ -23800,7 +23804,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23870,7 +23874,7 @@
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -23903,32 +23907,36 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N190" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23936,7 +23944,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23960,17 +23968,17 @@
       </c>
       <c r="X190" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA190" s="2" t="inlineStr">
@@ -23980,17 +23988,17 @@
       </c>
       <c r="AB190" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -24023,32 +24031,36 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N191" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -24056,7 +24068,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24080,17 +24092,17 @@
       </c>
       <c r="X191" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA191" s="2" t="inlineStr">
@@ -24100,17 +24112,17 @@
       </c>
       <c r="AB191" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC191" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -24143,32 +24155,36 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N192" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -24176,7 +24192,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24200,17 +24216,17 @@
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA192" s="2" t="inlineStr">
@@ -24220,17 +24236,17 @@
       </c>
       <c r="AB192" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -24263,32 +24279,36 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N193" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24296,7 +24316,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24320,17 +24340,17 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA193" s="2" t="inlineStr">
@@ -24340,17 +24360,17 @@
       </c>
       <c r="AB193" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -24416,7 +24436,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24470,7 +24490,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -24536,7 +24556,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24656,7 +24676,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24700,17 +24720,17 @@
       </c>
       <c r="AB196" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC196" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -24958,7 +24978,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -25082,7 +25102,7 @@
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -25206,7 +25226,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -25272,7 +25292,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25316,17 +25336,17 @@
       </c>
       <c r="AB201" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -25570,7 +25590,7 @@
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -25640,7 +25660,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25818,7 +25838,7 @@
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -26624,7 +26644,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26668,17 +26688,17 @@
       </c>
       <c r="AB212" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC212" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -26802,7 +26822,7 @@
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -27050,7 +27070,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -27174,7 +27194,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -27294,7 +27314,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -27418,7 +27438,7 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -27538,7 +27558,7 @@
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -27608,7 +27628,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27652,17 +27672,17 @@
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -27902,7 +27922,7 @@
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -27968,7 +27988,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -28886,7 +28906,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -29018,7 +29038,7 @@
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -29142,7 +29162,7 @@
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -29266,7 +29286,7 @@
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -29522,7 +29542,7 @@
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -30258,7 +30278,7 @@
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -30382,7 +30402,7 @@
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -30506,7 +30526,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -31374,7 +31394,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -31498,7 +31518,7 @@
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -31568,7 +31588,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q252" s="2" t="inlineStr">
@@ -31612,17 +31632,17 @@
       </c>
       <c r="AB252" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC252" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AD252" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -31746,7 +31766,7 @@
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -32308,7 +32328,7 @@
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q258" s="2" t="inlineStr">
@@ -32352,17 +32372,17 @@
       </c>
       <c r="AB258" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC258" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -32552,7 +32572,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32726,7 +32746,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -32970,7 +32990,7 @@
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -33218,7 +33238,7 @@
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -33342,7 +33362,7 @@
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -33466,7 +33486,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -33590,7 +33610,7 @@
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -33660,7 +33680,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33704,17 +33724,17 @@
       </c>
       <c r="AB269" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -34280,7 +34300,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34324,17 +34344,17 @@
       </c>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -34578,7 +34598,7 @@
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -34648,7 +34668,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
@@ -34822,7 +34842,7 @@
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -35190,7 +35210,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -35314,7 +35334,7 @@
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -35438,7 +35458,7 @@
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -35678,7 +35698,7 @@
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -35748,7 +35768,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35792,17 +35812,17 @@
       </c>
       <c r="AB286" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -36050,7 +36070,7 @@
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -36368,7 +36388,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q291" s="2" t="inlineStr">
@@ -36412,17 +36432,17 @@
       </c>
       <c r="AB291" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC291" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -36546,7 +36566,7 @@
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -36616,7 +36636,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36794,7 +36814,7 @@
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -36827,32 +36847,36 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K295" s="2" t="inlineStr"/>
       <c r="L295" s="2" t="inlineStr"/>
       <c r="M295" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N295" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N295" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O295" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -36860,7 +36884,7 @@
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q295" s="2" t="inlineStr">
@@ -36884,17 +36908,17 @@
       </c>
       <c r="X295" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y295" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z295" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA295" s="2" t="inlineStr">
@@ -36904,17 +36928,17 @@
       </c>
       <c r="AB295" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC295" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -36947,32 +36971,36 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K296" s="2" t="inlineStr"/>
       <c r="L296" s="2" t="inlineStr"/>
       <c r="M296" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N296" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N296" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O296" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -36980,7 +37008,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -37004,17 +37032,17 @@
       </c>
       <c r="X296" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y296" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z296" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA296" s="2" t="inlineStr">
@@ -37024,17 +37052,17 @@
       </c>
       <c r="AB296" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -37100,7 +37128,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
